--- a/artfynd/A 67089-2021 artfynd.xlsx
+++ b/artfynd/A 67089-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67089-2021 artfynd.xlsx
+++ b/artfynd/A 67089-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY154"/>
+  <dimension ref="A1:AY155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18265,6 +18265,112 @@
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>114964979</v>
+      </c>
+      <c r="B155" t="n">
+        <v>91213</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Renkullmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>446846</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7032735</v>
+      </c>
+      <c r="S155" t="n">
+        <v>50</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 67089-2021 artfynd.xlsx
+++ b/artfynd/A 67089-2021 artfynd.xlsx
@@ -18503,10 +18503,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119584559</v>
+        <v>119584929</v>
       </c>
       <c r="B157" t="n">
-        <v>90043</v>
+        <v>84009</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18519,21 +18519,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3286</v>
+        <v>5589</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18543,13 +18543,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>446966</v>
+        <v>446983</v>
       </c>
       <c r="R157" t="n">
-        <v>7032580</v>
+        <v>7032579</v>
       </c>
       <c r="S157" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18576,9 +18576,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18593,22 +18603,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
+          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119584929</v>
+        <v>119584559</v>
       </c>
       <c r="B158" t="n">
-        <v>84009</v>
+        <v>90043</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18621,21 +18631,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5589</v>
+        <v>3286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18645,13 +18655,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>446983</v>
+        <v>446966</v>
       </c>
       <c r="R158" t="n">
-        <v>7032579</v>
+        <v>7032580</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18678,19 +18688,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18705,12 +18705,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>

--- a/artfynd/A 67089-2021 artfynd.xlsx
+++ b/artfynd/A 67089-2021 artfynd.xlsx
@@ -18503,10 +18503,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119584929</v>
+        <v>119584559</v>
       </c>
       <c r="B157" t="n">
-        <v>84009</v>
+        <v>90043</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18519,21 +18519,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5589</v>
+        <v>3286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -18543,13 +18543,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>446983</v>
+        <v>446966</v>
       </c>
       <c r="R157" t="n">
-        <v>7032579</v>
+        <v>7032580</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18576,19 +18576,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18603,22 +18593,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
+          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119584559</v>
+        <v>119584929</v>
       </c>
       <c r="B158" t="n">
-        <v>90043</v>
+        <v>84009</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18631,21 +18621,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3286</v>
+        <v>5589</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18655,13 +18645,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>446966</v>
+        <v>446983</v>
       </c>
       <c r="R158" t="n">
-        <v>7032580</v>
+        <v>7032579</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18688,9 +18678,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18705,12 +18705,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Johan Staaf, Anders Hildingsson</t>
+          <t>Anders Hildingsson, Johan Staaf, Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>

--- a/artfynd/A 67089-2021 artfynd.xlsx
+++ b/artfynd/A 67089-2021 artfynd.xlsx
@@ -18285,7 +18285,7 @@
         <v>114964979</v>
       </c>
       <c r="B155" t="n">
-        <v>91641</v>
+        <v>91651</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>

--- a/artfynd/A 67089-2021 artfynd.xlsx
+++ b/artfynd/A 67089-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY190"/>
+  <dimension ref="A1:AZ190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101416603</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101416927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997672</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110022711</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112102682</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101397102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101400815</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415627</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001784</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104002734</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104004818</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101401957</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101400691</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551117</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2377,6 +2457,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013005</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2479,6 +2564,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551118</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2577,6 +2667,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101397729</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101401185</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101401510</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2881,6 +2986,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100585059</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2983,6 +3093,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399709</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3081,6 +3196,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101401505</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3178,6 +3298,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442196</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3275,6 +3400,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442197</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442198</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3469,6 +3604,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442199</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3567,6 +3707,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104134921</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3669,6 +3814,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551116</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3767,6 +3917,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103999404</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3864,6 +4019,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442229</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3962,6 +4122,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001806</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4075,6 +4240,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104005033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4189,6 +4359,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104057948</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4287,6 +4462,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101397586</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4413,6 +4593,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101400539</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4514,6 +4699,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101417128</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4612,6 +4802,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100584471</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4720,6 +4915,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996346</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4833,6 +5033,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104004270</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4931,6 +5136,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101404079</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5044,6 +5254,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995497</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5157,6 +5372,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995514</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5258,6 +5478,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104573</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5356,6 +5581,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111498</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5457,6 +5687,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120431881</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5558,6 +5793,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112102104</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5659,6 +5899,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104863</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5757,6 +6002,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100585169</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5870,6 +6120,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101402982</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5967,6 +6222,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442228</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6064,6 +6324,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551102</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6163,6 +6428,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399444</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6265,6 +6535,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101416911</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6366,6 +6641,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113335588</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6467,6 +6747,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112101944</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6568,6 +6853,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112102200</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6665,6 +6955,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119584559</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6762,6 +7057,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113326940</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6863,6 +7163,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112103325</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6964,6 +7269,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104270</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7061,6 +7371,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119585393</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7162,6 +7477,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113335591</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7263,6 +7583,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112101773</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7364,6 +7689,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104553</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7465,6 +7795,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114964979</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7562,6 +7897,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121929099</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7663,6 +8003,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111378</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7761,6 +8106,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111486</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7868,6 +8218,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119584929</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7969,6 +8324,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112102196</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8070,6 +8430,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104266</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8171,6 +8536,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111388</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8268,6 +8638,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213232</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8369,6 +8744,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112111398</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8467,6 +8847,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100572072</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8574,6 +8959,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100583905</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8672,6 +9062,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100585067</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8784,6 +9179,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101396142</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8897,6 +9297,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101402171</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9005,6 +9410,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101402894</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9102,6 +9512,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442238</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9199,6 +9614,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442239</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9296,6 +9716,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442240</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9393,6 +9818,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442241</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9490,6 +9920,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442242</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9587,6 +10022,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442243</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9684,6 +10124,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442244</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9781,6 +10226,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442245</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9878,6 +10328,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442246</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9975,6 +10430,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442247</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10072,6 +10532,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442248</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10185,6 +10650,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996865</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10298,6 +10768,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103999501</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10406,6 +10881,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001170</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10504,6 +10984,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001521</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10612,6 +11097,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001573</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10725,6 +11215,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104002084</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10833,6 +11328,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104004278</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10931,6 +11431,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100572004</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11044,6 +11549,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399830</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11157,6 +11667,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101402883</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11270,6 +11785,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995555</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11383,6 +11903,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996796</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11496,6 +12021,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103999561</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11604,6 +12134,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001569</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11717,6 +12252,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104004249</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11815,6 +12355,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101404083</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11928,6 +12473,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103994580</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12041,6 +12591,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995536</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12149,6 +12704,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104002087</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12246,6 +12806,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442231</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12354,6 +12919,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996915</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12452,6 +13022,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100585186</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12553,6 +13128,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101418047</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12663,6 +13243,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442218</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12773,6 +13358,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442219</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12883,6 +13473,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442220</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12993,6 +13588,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442221</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13103,6 +13703,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442222</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13213,6 +13818,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442224</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13316,6 +13926,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342670</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13419,6 +14034,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342771</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13522,6 +14142,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342870</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13627,6 +14252,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551100</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13736,6 +14366,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100584620</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13841,6 +14476,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399661</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13951,6 +14591,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415156</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14061,6 +14706,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101417038</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14171,6 +14821,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442202</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14281,6 +14936,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442203</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14404,6 +15064,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997531</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14517,6 +15182,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342229</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14620,6 +15290,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342350</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14723,6 +15398,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342556</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14826,6 +15506,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342709</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14929,6 +15614,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110342911</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15034,6 +15724,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551094</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15139,6 +15834,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551112</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15262,6 +15962,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758625</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15380,6 +16085,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101398855</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15492,6 +16202,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104002088</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15594,6 +16309,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101414561</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15696,6 +16416,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101416731</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15793,6 +16518,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442201</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15909,6 +16639,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110022775</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16006,6 +16741,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551092</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16104,6 +16844,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001891</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16206,6 +16951,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115179016</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16320,6 +17070,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101400021</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16428,6 +17183,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997685</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16536,6 +17296,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001030</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16635,6 +17400,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399432</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16738,6 +17508,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101403026</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16840,6 +17615,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415061</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16942,6 +17722,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415102</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17044,6 +17829,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415260</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17146,6 +17936,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415532</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17248,6 +18043,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101416613</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17350,6 +18150,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101417854</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17452,6 +18257,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101417865</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17554,6 +18364,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101417913</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17651,6 +18466,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442208</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17748,6 +18568,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442209</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17845,6 +18670,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442210</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17942,6 +18772,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442211</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18039,6 +18874,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442212</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18136,6 +18976,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442213</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18233,6 +19078,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442214</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18330,6 +19180,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101442216</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18441,6 +19296,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94258289</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18544,6 +19404,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100571606</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18646,6 +19511,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101414551</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18754,6 +19624,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001087</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18851,6 +19726,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551090</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18948,6 +19828,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551107</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19061,6 +19946,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101399845</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19169,6 +20059,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101402888</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19282,6 +20177,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995657</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19395,6 +20295,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103996859</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19503,6 +20408,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104001532</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19616,6 +20526,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104002105</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19729,6 +20644,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104004259</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19830,6 +20750,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101415314</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19931,6 +20856,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101418038</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20044,6 +20974,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103994592</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20145,6 +21080,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101414952</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20258,6 +21198,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995599</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20359,8 +21304,204 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112104547</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>